--- a/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRSectionExposureInformationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
